--- a/excel_routes/route_ATZ_ELQ_threats.xlsx
+++ b/excel_routes/route_ATZ_ELQ_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6244</v>
+        <v>6276</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8798</v>
+        <v>8843</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2554</v>
+        <v>-2567</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -560,6 +560,51 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>28-MAR-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>15839</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>16170</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-331</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
